--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_147_R15.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_147_R15.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.9319</v>
+        <v>7.4353</v>
       </c>
       <c r="E2" t="n">
-        <v>4.824</v>
+        <v>4.8986</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1079</v>
+        <v>2.5366</v>
       </c>
       <c r="G2" t="n">
         <v>3.2779</v>
@@ -610,13 +610,13 @@
         <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2596</v>
+        <v>-0.237</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2592</v>
+        <v>-0.1845</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5188</v>
+        <v>-0.0525</v>
       </c>
       <c r="V2" t="n">
         <v>2.5387</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.866</v>
+        <v>3.0427</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6199</v>
+        <v>1.5949</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2461</v>
+        <v>1.4477</v>
       </c>
       <c r="G3" t="n">
         <v>2.3735</v>
@@ -688,13 +688,13 @@
         <v>3.4793</v>
       </c>
       <c r="S3" t="n">
-        <v>-3.8992</v>
+        <v>-2.7226</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.867</v>
+        <v>-0.892</v>
       </c>
       <c r="U3" t="n">
-        <v>-2.0322</v>
+        <v>-1.8306</v>
       </c>
       <c r="V3" t="n">
         <v>1.0722</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6457</v>
+        <v>0.7067</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9716</v>
+        <v>2.8981</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.3259</v>
+        <v>-2.1914</v>
       </c>
       <c r="G4" t="n">
         <v>0.0914</v>
@@ -766,13 +766,13 @@
         <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4462</v>
+        <v>0.5072</v>
       </c>
       <c r="T4" t="n">
-        <v>1.9856</v>
+        <v>0.9122</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5395</v>
+        <v>-0.405</v>
       </c>
       <c r="V4" t="n">
         <v>-0.8197</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. TARPEY</t>
+          <t>M. STRAZEL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.7131</v>
+        <v>-0.1792</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9797</v>
+        <v>1.1407</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.6928</v>
+        <v>-1.3199</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1147</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9747</v>
+        <v>-1.7296</v>
       </c>
       <c r="I5" t="n">
-        <v>0.86</v>
+        <v>1.663</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2114</v>
+        <v>1.2959</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0336</v>
+        <v>0.2051</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1778</v>
+        <v>1.0907</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3261</v>
+        <v>-1.3625</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0083</v>
+        <v>-1.9348</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3178</v>
+        <v>0.5723</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.3195</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.6486</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3734</v>
+        <v>0.02</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2249</v>
+        <v>-0.6686</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1418</v>
+        <v>2.1444</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1418</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. STRAZEL</t>
+          <t>T. TARPEY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0857</v>
+        <v>-0.504</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6375</v>
+        <v>1.0544</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.7232</v>
+        <v>-1.5584</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.06660000000000001</v>
+        <v>-0.1147</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.7296</v>
+        <v>-0.9747</v>
       </c>
       <c r="I6" t="n">
-        <v>1.663</v>
+        <v>0.86</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2959</v>
+        <v>1.2114</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2051</v>
+        <v>0.0336</v>
       </c>
       <c r="L6" t="n">
-        <v>1.0907</v>
+        <v>1.1778</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3625</v>
+        <v>-1.3261</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.9348</v>
+        <v>-1.0083</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5723</v>
+        <v>-0.3178</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3195</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5551</v>
+        <v>-0.3892</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4832</v>
+        <v>-0.2987</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.0719</v>
+        <v>-0.0905</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.1444</v>
+        <v>0.1418</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.6083</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. BLOSSOMGAME</t>
+          <t>D. THEIS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5644</v>
+        <v>-2.0096</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7405</v>
+        <v>-3.7164</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.824</v>
+        <v>1.7067</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.9154</v>
+        <v>-0.4268</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2664</v>
+        <v>-0.8485</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.649</v>
+        <v>0.4217</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.7426</v>
+        <v>-1.3412</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007</v>
+        <v>0.1211</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-1.4623</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1729</v>
+        <v>0.9143</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2734</v>
+        <v>-0.9696</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1005</v>
+        <v>1.884</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8556</v>
+        <v>2.3195</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5856</v>
+        <v>-2.5132</v>
       </c>
       <c r="T7" t="n">
-        <v>1.9505</v>
+        <v>-1.1279</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.3649</v>
+        <v>-1.3853</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9304</v>
+        <v>0.9304</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.7886</v>
+        <v>1.0722</v>
       </c>
       <c r="X7" t="n">
         <v>-0.1418</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. THEIS</t>
+          <t>J. BLOSSOMGAME</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4313</v>
+        <v>-3.4031</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.3061</v>
+        <v>-2.4783</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8748</v>
+        <v>-0.9248</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4268</v>
+        <v>-1.9154</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8485</v>
+        <v>-1.2664</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4217</v>
+        <v>-0.649</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.3412</v>
+        <v>-0.7426</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1211</v>
+        <v>0.007</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.4623</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9143</v>
+        <v>-1.1729</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9696</v>
+        <v>-1.2734</v>
       </c>
       <c r="O8" t="n">
-        <v>1.884</v>
+        <v>0.1005</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3195</v>
+        <v>1.8556</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.935</v>
+        <v>-1.2531</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.7177</v>
+        <v>0.2126</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.2173</v>
+        <v>-1.4657</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9304</v>
+        <v>-0.9304</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0722</v>
+        <v>-0.7886</v>
       </c>
       <c r="X8" t="n">
         <v>-0.1418</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.8015</v>
+        <v>-3.937</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.2365</v>
+        <v>-3.3047</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.6322</v>
       </c>
       <c r="G9" t="n">
         <v>-5.4082</v>
@@ -1156,13 +1156,13 @@
         <v>2.5515</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.3237</v>
+        <v>-2.4592</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.5683</v>
+        <v>-0.6366000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.7554</v>
+        <v>-1.8226</v>
       </c>
       <c r="V9" t="n">
         <v>2.5387</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.219</v>
+        <v>-5.403</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.1636</v>
+        <v>-6.3812</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9445</v>
+        <v>0.9781</v>
       </c>
       <c r="G10" t="n">
         <v>-3.0143</v>
@@ -1234,13 +1234,13 @@
         <v>3.2473</v>
       </c>
       <c r="S10" t="n">
-        <v>-3.5632</v>
+        <v>-2.7472</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.7924</v>
+        <v>-1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.7708</v>
+        <v>-1.7372</v>
       </c>
       <c r="V10" t="n">
         <v>1.7501</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.371399999999999</v>
+        <v>-4.2512</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.414000000000001</v>
+        <v>-4.293900000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0424000000000001</v>
+        <v>0.04240000000000044</v>
       </c>
       <c r="G11" t="n">
         <v>-5.203200000000001</v>
@@ -1282,16 +1282,16 @@
         <v>-11.4938</v>
       </c>
       <c r="I11" t="n">
-        <v>6.290900000000001</v>
+        <v>6.2909</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.034699999999999</v>
+        <v>-1.0347</v>
       </c>
       <c r="K11" t="n">
         <v>-2.1213</v>
       </c>
       <c r="L11" t="n">
-        <v>1.086599999999999</v>
+        <v>1.0866</v>
       </c>
       <c r="M11" t="n">
         <v>-4.168600000000001</v>
@@ -1312,13 +1312,13 @@
         <v>18.5561</v>
       </c>
       <c r="S11" t="n">
-        <v>-13.5831</v>
+        <v>-12.4629</v>
       </c>
       <c r="T11" t="n">
-        <v>-4.1251</v>
+        <v>-3.0049</v>
       </c>
       <c r="U11" t="n">
-        <v>-9.4581</v>
+        <v>-9.458</v>
       </c>
       <c r="V11" t="n">
         <v>7.616099999999999</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.3843</v>
+        <v>7.2884</v>
       </c>
       <c r="E12" t="n">
-        <v>6.3566</v>
+        <v>5.0591</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0277</v>
+        <v>2.2293</v>
       </c>
       <c r="G12" t="n">
         <v>3.9602</v>
@@ -1390,13 +1390,13 @@
         <v>1.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>2.8906</v>
+        <v>1.7948</v>
       </c>
       <c r="T12" t="n">
-        <v>3.1181</v>
+        <v>1.8207</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2275</v>
+        <v>-0.0259</v>
       </c>
       <c r="V12" t="n">
         <v>0.1418</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.7792</v>
+        <v>6.048</v>
       </c>
       <c r="E13" t="n">
         <v>2.6509</v>
       </c>
       <c r="F13" t="n">
-        <v>3.1282</v>
+        <v>3.3971</v>
       </c>
       <c r="G13" t="n">
         <v>5.584</v>
@@ -1468,13 +1468,13 @@
         <v>1.6237</v>
       </c>
       <c r="S13" t="n">
-        <v>1.744</v>
+        <v>2.0129</v>
       </c>
       <c r="T13" t="n">
         <v>1.2151</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5289</v>
+        <v>0.7978</v>
       </c>
       <c r="V13" t="n">
         <v>1.4665</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3374</v>
+        <v>2.8847</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5574</v>
+        <v>0.9112</v>
       </c>
       <c r="F14" t="n">
-        <v>2.78</v>
+        <v>1.9734</v>
       </c>
       <c r="G14" t="n">
         <v>1.0858</v>
@@ -1546,13 +1546,13 @@
         <v>1.8556</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3986</v>
+        <v>1.9459</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0553</v>
+        <v>0.4092</v>
       </c>
       <c r="U14" t="n">
-        <v>2.3432</v>
+        <v>1.5367</v>
       </c>
       <c r="V14" t="n">
         <v>-2.0026</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3476</v>
+        <v>1.1618</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9687</v>
+        <v>1.6149</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6211</v>
+        <v>-0.4531</v>
       </c>
       <c r="G15" t="n">
         <v>2.5031</v>
@@ -1624,13 +1624,13 @@
         <v>1.6237</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9167</v>
+        <v>1.7308</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7774</v>
+        <v>1.4235</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1393</v>
+        <v>0.3073</v>
       </c>
       <c r="V15" t="n">
         <v>-2.1444</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.463</v>
+        <v>0.8502999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.2772</v>
+        <v>-1.3336</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8142</v>
+        <v>2.1838</v>
       </c>
       <c r="G16" t="n">
         <v>0.8367</v>
@@ -1702,13 +1702,13 @@
         <v>2.0876</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4863</v>
+        <v>1.7996</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0553</v>
+        <v>0.999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.431</v>
+        <v>0.8006</v>
       </c>
       <c r="V16" t="n">
         <v>-0.3943</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. BACOT JR.</t>
+          <t>W. BALDWIN IV</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8557</v>
+        <v>-1.4993</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5281</v>
+        <v>-1.4804</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3838</v>
+        <v>-0.0189</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1761</v>
+        <v>-0.7212</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.1091</v>
+        <v>0.6541</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.067</v>
+        <v>-1.3754</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3645</v>
+        <v>-0.2812</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7191</v>
+        <v>0.6693</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3546</v>
+        <v>-0.9505</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8116</v>
+        <v>-0.44</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.39</v>
+        <v>-0.0152</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4216</v>
+        <v>-0.4248</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.232</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.232</v>
+        <v>-3.7112</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.8556</v>
       </c>
       <c r="S17" t="n">
-        <v>1.6245</v>
+        <v>0.9357</v>
       </c>
       <c r="T17" t="n">
-        <v>1.1246</v>
+        <v>1.1562</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4999</v>
+        <v>-0.2205</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.3558</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. BIBEROVIC</t>
+          <t>A. BACOT JR.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.6996</v>
+        <v>-1.5799</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.2589</v>
+        <v>-0.0616</v>
       </c>
       <c r="F18" t="n">
-        <v>2.5593</v>
+        <v>-1.5183</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.0099</v>
+        <v>-1.1761</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8393</v>
+        <v>-1.1091</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1706</v>
+        <v>-0.067</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.0536</v>
+        <v>-0.3645</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.4145</v>
+        <v>-0.7191</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6391</v>
+        <v>0.3546</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0437</v>
+        <v>-0.8116</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5752</v>
+        <v>-0.39</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4685</v>
+        <v>-0.4216</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.4639</v>
+        <v>-0.232</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.3195</v>
+        <v>-0.232</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8556</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3825</v>
+        <v>0.9003</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1142</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>1.2683</v>
+        <v>0.3655</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.6083</v>
+        <v>-1.0722</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.6083</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. BOSTON JR.</t>
+          <t>M. BIRSEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7057</v>
+        <v>-1.6104</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1602</v>
+        <v>-0.0631</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.866</v>
+        <v>-1.5473</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.6984</v>
+        <v>-1.0449</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1224</v>
+        <v>-0.5029</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.576</v>
+        <v>-0.542</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.5188</v>
+        <v>0.0704</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7324000000000001</v>
+        <v>0.0336</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7863</v>
+        <v>0.0368</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1796</v>
+        <v>-1.1153</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.39</v>
+        <v>-0.5365</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7896</v>
+        <v>-0.5788</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.232</v>
       </c>
       <c r="R19" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.5288</v>
+        <v>0.2025</v>
       </c>
       <c r="T19" t="n">
-        <v>1.9109</v>
+        <v>0.0984</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3822</v>
+        <v>0.1041</v>
       </c>
       <c r="V19" t="n">
         <v>-0.5361</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. BIRSEN</t>
+          <t>T. BIBEROVIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.015</v>
+        <v>-1.8841</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5349</v>
+        <v>-4.1409</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4801</v>
+        <v>2.2568</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0449</v>
+        <v>-1.0099</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5029</v>
+        <v>-0.8393</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.542</v>
+        <v>-0.1706</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0704</v>
+        <v>-2.0536</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0336</v>
+        <v>-1.4145</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0368</v>
+        <v>-0.6391</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1153</v>
+        <v>1.0437</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5365</v>
+        <v>0.5752</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5788</v>
+        <v>0.4685</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.232</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.232</v>
+        <v>-2.3195</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.8556</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2021</v>
+        <v>1.198</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3734</v>
+        <v>0.2322</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1713</v>
+        <v>0.9658</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5361</v>
+        <v>-1.6083</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5361</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>W. BALDWIN IV</t>
+          <t>B. BOSTON JR.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1056</v>
+        <v>-2.1611</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9522</v>
+        <v>-0.4295</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1534</v>
+        <v>-1.7315</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7212</v>
+        <v>-2.6984</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6541</v>
+        <v>-1.1224</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.3754</v>
+        <v>-1.576</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2812</v>
+        <v>-1.5188</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6693</v>
+        <v>-0.7324000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.9505</v>
+        <v>-0.7863</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.44</v>
+        <v>-1.1796</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0152</v>
+        <v>-0.39</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4248</v>
+        <v>-0.7896</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.8556</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.7112</v>
+        <v>-0.232</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8556</v>
+        <v>0.232</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3295</v>
+        <v>1.0734</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6844</v>
+        <v>1.3212</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3549</v>
+        <v>-0.2478</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1418</v>
+        <v>-0.5361</v>
       </c>
       <c r="W21" t="n">
-        <v>1.3558</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.214</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.6323</v>
+        <v>-4.1269</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.6356</v>
+        <v>-3.1638</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9967</v>
+        <v>-0.9631</v>
       </c>
       <c r="G22" t="n">
         <v>-2.1161</v>
@@ -2170,13 +2170,13 @@
         <v>0.232</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5162</v>
+        <v>-0.0108</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.224</v>
+        <v>0.2478</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2921</v>
+        <v>-0.2585</v>
       </c>
       <c r="V22" t="n">
         <v>-1.0722</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>5.371600000000002</v>
+        <v>5.3715</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.436900000000001</v>
+        <v>-0.4367999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>5.808299999999999</v>
+        <v>5.8082</v>
       </c>
       <c r="G23" t="n">
         <v>5.203200000000001</v>
@@ -2218,16 +2218,16 @@
         <v>11.4941</v>
       </c>
       <c r="I23" t="n">
-        <v>-6.290900000000001</v>
+        <v>-6.2909</v>
       </c>
       <c r="J23" t="n">
         <v>4.1686</v>
       </c>
       <c r="K23" t="n">
-        <v>9.372699999999998</v>
+        <v>9.3727</v>
       </c>
       <c r="L23" t="n">
-        <v>-5.204000000000001</v>
+        <v>-5.204</v>
       </c>
       <c r="M23" t="n">
         <v>1.0347</v>
@@ -2248,13 +2248,13 @@
         <v>12.7575</v>
       </c>
       <c r="S23" t="n">
-        <v>13.5832</v>
+        <v>13.5831</v>
       </c>
       <c r="T23" t="n">
-        <v>9.457899999999999</v>
+        <v>9.4581</v>
       </c>
       <c r="U23" t="n">
-        <v>4.1252</v>
+        <v>4.125100000000001</v>
       </c>
       <c r="V23" t="n">
         <v>-7.616100000000001</v>
